--- a/tame_output/ON/bt/strategyON_20230816.xlsx
+++ b/tame_output/ON/bt/strategyON_20230816.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.6%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>103.0%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>139.7%</t>
+          <t>139.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>134.2%</t>
+          <t>133.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1690"/>
+  <dimension ref="A1:G1691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40380,7 +40380,7 @@
         <v>45152</v>
       </c>
       <c r="B1690" t="n">
-        <v>2.885216451676505</v>
+        <v>2.885577337134999</v>
       </c>
       <c r="C1690" t="n">
         <v>2.989232987685216</v>
@@ -40396,6 +40396,29 @@
       </c>
       <c r="G1690" t="n">
         <v>4.294075620471082</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="2" t="n">
+        <v>45153</v>
+      </c>
+      <c r="B1691" t="n">
+        <v>2.87949509783155</v>
+      </c>
+      <c r="C1691" t="n">
+        <v>2.979269203333789</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>1.548564311686945</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>3.598338503694821</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>2.176712241264047</v>
+      </c>
+      <c r="G1691" t="n">
+        <v>4.285296548092218</v>
       </c>
     </row>
   </sheetData>
